--- a/tables/Alcohol_Tier1_HedgesG.xlsx
+++ b/tables/Alcohol_Tier1_HedgesG.xlsx
@@ -613,32 +613,54 @@
         <v>1970</v>
       </c>
       <c r="C4" t="n">
-        <v>81</v>
+        <v>158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+          <t>LSD</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Chi-squared</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1.408</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>chi2</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>excluded</t>
+          <t>approx</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>No outcome statistic reported</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+          <t>χ²=1.408, p&gt;0.05; 24% vs 27% good adjustment; treatment direction slightly negative</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>-0.1896472447721773</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-0.1887340156641251</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.02542917888819211</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.1594652905437171</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-0.5012859851298106</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.1238179538015604</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">

--- a/tables/Alcohol_Tier1_HedgesG.xlsx
+++ b/tables/Alcohol_Tier1_HedgesG.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O34"/>
+  <dimension ref="A1:O33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -583,7 +583,11 @@
           <t>clean</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Authors report Hedges' g = 0.52 (95% CI 0.11-0.94) directly for the primary PHDD between-group contrast at weeks 5-36 (Table 2/Efficacy text); this is a direct pass-through of an author-computed Hedges g, no conversion required. Article's own convention already orients positive g toward the favored (psilocybin) direction, so direction=1.</t>
+        </is>
+      </c>
       <c r="J3" t="n">
         <v>0.52</v>
       </c>
@@ -694,12 +698,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>approx</t>
+          <t>clean</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>F is interaction term with large df_error; rough</t>
+          <t>Primary outcome (21-day alcohol abstinence) tested via the time-by-treatment interaction, F(1,797)=25.1, p&lt;.001 (single-numerator-df F, directly convertible to a Hedges' g equivalent); direction=1 because the effect favors ketamine, the psychedelic arm.</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -731,7 +735,7 @@
         <v>2019</v>
       </c>
       <c r="C6" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -761,40 +765,46 @@
         <v>1.05907456038554</v>
       </c>
       <c r="K6" t="n">
-        <v>1.050022641066006</v>
+        <v>1.030450923618364</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0505697085930624</v>
+        <v>0.1510304850997657</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2248770966396142</v>
+        <v>0.3886264081348123</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6092635316523622</v>
+        <v>0.2687431636741319</v>
       </c>
       <c r="O6" t="n">
-        <v>1.49078175047965</v>
+        <v>1.792158683562596</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Denson 1970</t>
+          <t>Dusen 1967</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1970</v>
-      </c>
-      <c r="C7" t="n">
-        <v>51</v>
-      </c>
+        <v>1967</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>LSD</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Non-significant (no statistic)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>4.03 vs 3.97 (18-month mean outcome score, 2=worse...5=much improved scale; prelysergide control N=37 vs Lysergide Experiment N=56)</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
@@ -803,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>No outcome statistic reported</t>
+          <t>Group means without SDs; ns</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -816,59 +826,73 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Dusen 1967</t>
+          <t>Gent 2024</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1967</v>
+        <v>2024</v>
       </c>
       <c r="C8" t="n">
-        <v>99</v>
+        <v>28</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LSD</t>
+          <t>Ketamine</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Group means (Tx vs Ctrl)</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>3.97 vs 4.03</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>excluded</t>
+          <t>clean</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Group means without SDs; ns</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+          <t>Primary outcome (psychological engagement in MBI) tested via the group main effect, F(1,26)=6.88, p=.014, a single-numerator-df F cleanly convertible to a Hedges' g equivalent; direction=1 because the effect favors esketamine (the psychedelic arm) over placebo.</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1.028815599833876</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.9988500969260934</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.1606732413594512</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.4008406682953355</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.2132023870672358</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.784497806784951</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Gent 2024</t>
+          <t>Grabski 2022</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="C9" t="n">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -877,11 +901,11 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Mean difference (percentage days abstinent, %), site-adjusted intention-to-treat, ketamine vs. placebo pooled across therapy conditions at 6 months</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>6.45</v>
+        <v>10.1</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
@@ -891,7 +915,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>F has 2 df numerator (3-arm); not 1-df comparison</t>
+          <t>Mean difference reported without SDs</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -904,27 +928,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Grabski 2022</t>
+          <t>Heinzerling 2023</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C10" t="n">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ketamine</t>
+          <t>Psilocybin</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mean difference (%)</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>10.1</v>
+        <v>15.76</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
@@ -934,7 +958,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Mean difference reported without SDs</t>
+          <t>F has 6 df numerator; repeated-measures design</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -947,18 +971,18 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Heinzerling 2023</t>
+          <t>Hollister 1969</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2023</v>
+        <v>1969</v>
       </c>
       <c r="C11" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Psilocybin</t>
+          <t>LSD</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -967,37 +991,53 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>15.76</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
+        <v>8.5</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>excluded</t>
+          <t>clean</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>F has 6 df numerator; repeated-measures design</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
+          <t>Sig. F unfavorable to LSD vs dextroamphetamine</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>-0.8246211251235321</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-0.8101540878406631</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.09618166273383263</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.3101316861170955</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-1.41801219263017</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-0.202295983051156</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Hollister 1969</t>
+          <t>Jensen 1963</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1969</v>
+        <v>1963</v>
       </c>
       <c r="C12" t="n">
-        <v>45</v>
+        <v>91</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1006,45 +1046,31 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
+          <t>Two-group proportions (%)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>63 vs 27</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>clean</t>
+          <t>excluded</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Sig. F unfavorable to LSD vs dextroamphetamine</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>-0.8246211251235321</v>
-      </c>
-      <c r="K12" t="n">
-        <v>-0.8101540878406631</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.09618166273383263</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.3101316861170955</v>
-      </c>
-      <c r="N12" t="n">
-        <v>-1.41801219263017</v>
-      </c>
-      <c r="O12" t="n">
-        <v>-0.202295983051156</v>
-      </c>
+          <t>Two-group proportions; downgrade to Tier 2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1104,15 +1130,13 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jensen 1963</t>
+          <t>Johnson 1969</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1963</v>
-      </c>
-      <c r="C14" t="n">
-        <v>91</v>
-      </c>
+        <v>1969</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>LSD</t>
@@ -1120,14 +1144,10 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Two-group proportions (%)</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>63 vs 27</t>
-        </is>
-      </c>
+          <t>Non-significant (no statistic)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
@@ -1136,7 +1156,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Two-group proportions; downgrade to Tier 2</t>
+          <t>Reported only as "NS"</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -1149,14 +1169,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Johnson 1969</t>
+          <t>Kurland 1967</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1969</v>
+        <v>1967</v>
       </c>
       <c r="C15" t="n">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1165,7 +1185,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Non-significant (no statistic)</t>
+          <t>Abstinence rate (%), single-arm</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -1177,7 +1197,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Reported only as "NS"</t>
+          <t>Single-arm rate; no comparator</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -1190,27 +1210,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Kurland 1967</t>
+          <t>Luquiens 2025</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1967</v>
+        <v>2025</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LSD</t>
+          <t>Psilocybin</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Abstinence rate (%)</t>
+          <t>Risk difference (%)</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>33.3</v>
+        <v>-44</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
@@ -1220,7 +1240,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Single-arm rate; no comparator</t>
+          <t>Risk difference only; downgrade to Tier 2</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -1233,27 +1253,29 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Luquiens 2025</t>
+          <t>MacLean 1961</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2025</v>
+        <v>1961</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Psilocybin</t>
+          <t>LSD</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Risk difference (%)</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>-44</v>
+          <t>Single-arm improvement rate (%)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>46/61 (75.4%)</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
@@ -1263,7 +1285,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Risk difference only; downgrade to Tier 2</t>
+          <t>Single-arm improvement rate</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -1276,28 +1298,26 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MacLean 1961</t>
+          <t>Marvania 2024</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1961</v>
+        <v>2024</v>
       </c>
       <c r="C18" t="n">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LSD</t>
+          <t>Ketamine</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Improvement rate (%)</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>49</v>
-      </c>
+          <t>Paired t-test (within-subjects, no comparator arm)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
@@ -1306,7 +1326,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Single-arm improvement rate</t>
+          <t>Within-group AASE change; no comparator</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -1319,126 +1339,130 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marvania 2024</t>
+          <t>Nicholas 2022</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="C19" t="n">
-        <v>18</v>
+        <v>82</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Ketamine</t>
+          <t>MDMA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Within-group change (%)</t>
+          <t>Hedges' g</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>51.98</v>
-      </c>
-      <c r="G19" t="inlineStr"/>
+        <v>0.45</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>excluded</t>
+          <t>clean</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Within-group AASE change; no comparator</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
+          <t>Authors directly report Hedge's g=.45 for the AUDIT (alcohol) change-score group difference, MDMA-AT vs Placebo+Therapy (Abstract; §3.2); this is a direct pass-through of an author-computed Hedges' g requiring no conversion, and the reported positive value already favors MDMA-AT (greater alcohol-use reduction), so direction=1.</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.05001524390243903</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.223640881554422</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.01166387215333281</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.8883361278466673</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nicholas 2022</t>
+          <t>O'Reilly 1964</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2022</v>
+        <v>1964</v>
       </c>
       <c r="C20" t="n">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MDMA</t>
+          <t>LSD</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hedges' g</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
+          <t>Abstinence rate (%)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>38% (26/68)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>clean</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0.05001524390243903</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0.223640881554422</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0.01166387215333281</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0.8883361278466673</v>
-      </c>
+          <t>excluded</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Single-arm abstinence rate</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>O'Reilly 1964</t>
+          <t>Pagni 2024</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1964</v>
+        <v>2024</v>
       </c>
       <c r="C21" t="n">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LSD</t>
+          <t>Psilocybin</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Abstinence rate (%)</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>38</v>
-      </c>
+          <t>Whole-brain fMRI cluster-level statistics (multiple discrete clusters comprising the primary outcome; no single scalar effect size)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
@@ -1447,7 +1471,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Single-arm abstinence rate</t>
+          <t>Within-subjects t (df=3); not between-groups</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -1480,7 +1504,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1498,48 +1522,50 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>0.5487032611687345</v>
+        <v>0.5052911526399113</v>
       </c>
       <c r="K22" t="n">
-        <v>0.5436692862956268</v>
+        <v>0.5006554539918388</v>
       </c>
       <c r="L22" t="n">
-        <v>0.04937843031464997</v>
+        <v>0.04911104692626056</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2222125791098469</v>
+        <v>0.2216101236998449</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1081326312403269</v>
+        <v>0.06629961154014274</v>
       </c>
       <c r="O22" t="n">
-        <v>0.9792059413509268</v>
+        <v>0.9350112964435348</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Pagni 2024</t>
+          <t>Pahnke 1970</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2024</v>
+        <v>1970</v>
       </c>
       <c r="C23" t="n">
-        <v>11</v>
+        <v>104</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Psilocybin</t>
+          <t>LSD</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>5.568</v>
+          <t>Two-group proportions (%)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>53 vs 33</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
@@ -1549,7 +1575,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Within-subjects t (df=3); not between-groups</t>
+          <t>Two dose-group proportions; downgrade to Tier 2</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
@@ -1562,161 +1588,165 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pahnke 1970</t>
+          <t>Rieser 2025</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1970</v>
+        <v>2025</v>
       </c>
       <c r="C24" t="n">
-        <v>104</v>
+        <v>37</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LSD</t>
+          <t>Psilocybin</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Two-group proportions (%)</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>53 vs 33</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
+          <t>Cohen's d</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>d</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>excluded</t>
+          <t>clean</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Two dose-group proportions; downgrade to Tier 2</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
+          <t>Cohen's d = 0.151 for abstinence duration (psilocybin vs. placebo, 4-week follow-up) is directly reported by the authors and requires no derivation, so it is a clean d-to-Hedges'-g pass-through. Flagging for human awareness: this same d-value is paired with two different p-values in the article (p=0.55 in the Abstract vs. p=0.37 in the Results narrative) - an unresolved internal inconsistency in the source article that does not affect the d-value itself but affects interpretation of its significance.</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.1477410071942446</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.1084030730433347</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.3292462194822208</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.4975815829909082</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.7930635973793974</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rieser 2025</t>
+          <t>Rothberg 2021</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="C25" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Psilocybin</t>
+          <t>Ketamine</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cohen's d</t>
+          <t>Odds ratio (approximate)</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0.151</v>
+        <v>2.98</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>OR</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>clean</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>approx</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>OR reported as approx (~5); no cell counts [from 23.5% vs 47.8% (Table 2: ketamine 4/17 vs midazolam 11/23 engaged in at-risk drinking post-infusion)]</t>
+        </is>
+      </c>
       <c r="J25" t="n">
-        <v>0.151</v>
+        <v>-0.6020088671595277</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1477410071942446</v>
+        <v>-0.5900484260901332</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1084030730433347</v>
+        <v>0.1043519643141431</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3292462194822208</v>
+        <v>0.3230355465179383</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.4975815829909082</v>
+        <v>-1.223198097265292</v>
       </c>
       <c r="O25" t="n">
-        <v>0.7930635973793974</v>
+        <v>0.04310124508502577</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rothberg 2020</t>
+          <t>Sessa 2019</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C26" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Ketamine</t>
+          <t>MDMA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Odds ratio</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>5</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>OR</t>
-        </is>
-      </c>
+          <t>Single-arm rate (no inferential statistic)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>4/4 (100%) tolerated; 2/4 alcohol-free, 2/4 single low-dose lapse only</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>approx</t>
+          <t>excluded</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>OR reported as approx (~5); no cell counts</t>
-        </is>
-      </c>
-      <c r="J26" t="n">
-        <v>0.8873296265122473</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0.8670091007142569</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0.1250243540103049</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0.353587830687518</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0.1739769525667215</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.560041248861792</v>
-      </c>
+          <t>Case series 2/4 abstinent; no comparator</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1737,14 +1767,10 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Within-group mean change</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>18.7 vs 130.6</t>
-        </is>
-      </c>
+          <t>Descriptive completion/safety rate (no inferential statistic)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
@@ -1766,27 +1792,29 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sessa 2019</t>
+          <t>Smart 1966</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2019</v>
+        <v>1966</v>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>MDMA</t>
+          <t>LSD</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Abstinence rate (%)</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>50</v>
+          <t>Non-significant 3-group ANOVA (multi-df F) — percentage gain in abstinence</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>34 vs 32 vs 20 (%, lysergide vs ephedrine vs control)</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
@@ -1796,7 +1824,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Case series 2/4 abstinent; no comparator</t>
+          <t>Two-group proportions; downgrade to Tier 2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -1809,14 +1837,14 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Smart 1966</t>
+          <t>Smith 1958</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1966</v>
+        <v>1958</v>
       </c>
       <c r="C29" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1825,12 +1853,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Two-group proportions (%)</t>
+          <t>Single-arm improvement rate (%)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>33.7 vs 19.6</t>
+          <t>12/24 (50%)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -1841,7 +1869,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Two-group proportions; downgrade to Tier 2</t>
+          <t>Single-arm improvement rate</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -1854,249 +1882,206 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Smith 1958</t>
+          <t>Terasaki 2022</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1958</v>
+        <v>2022</v>
       </c>
       <c r="C30" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LSD</t>
+          <t>Ketamine</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Improvement rate (%)</t>
+          <t>Risk ratio</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>50</v>
-      </c>
-      <c r="G30" t="inlineStr"/>
+        <v>0.37</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>excluded</t>
+          <t>approx</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Single-arm improvement rate</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
+          <t>RR=0.37 = LESS readmission (favors ketamine); sign flipped</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>0.5481600076332798</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.5333448722918398</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.1380742792133333</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.3715834754309364</v>
+      </c>
+      <c r="N30" t="n">
+        <v>-0.1949587395527955</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.261648484136475</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Terasaki 2022</t>
+          <t>Thurgur 2025</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="C31" t="n">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Ketamine</t>
+          <t>MDMA</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Risk ratio</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>RR</t>
-        </is>
-      </c>
+          <t>Bayesian posterior probability (single-arm binomial success rate)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>9/14 (Bayesian posterior probability of treatment success: 0.63 flat prior, 0.55 skeptical prior)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>approx</t>
+          <t>excluded</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>RR=0.37 = LESS readmission (favors ketamine); sign flipped</t>
-        </is>
-      </c>
-      <c r="J31" t="n">
-        <v>0.5481600076332798</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0.5383128218674125</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0.09420205334303246</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0.3069235301227856</v>
-      </c>
-      <c r="N31" t="n">
-        <v>-0.06325729717324724</v>
-      </c>
-      <c r="O31" t="n">
-        <v>1.139882940908072</v>
-      </c>
+          <t>Bayesian posterior not directly convertible</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Thurgur 2025</t>
+          <t>Tomsovic 1970</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2025</v>
+        <v>1970</v>
       </c>
       <c r="C32" t="n">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>MDMA</t>
+          <t>LSD</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bayesian posterior probability</t>
+          <t>Chi-squared</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="G32" t="inlineStr"/>
+        <v>7.19</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>chi2</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>excluded</t>
+          <t>clean</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Bayesian posterior not directly convertible</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
+          <t>χ²(1)=7.19 (Table 7) comparing nonschizophrenic lysergide-treated (n=32) vs. nonschizophrenic control group I (n=26) on 1-year abstinence/nonabstinence classification. The article explicitly states the applicable critical value is for df=1 ('Chi square for .05 level of confidence with df 1 = 3.84'), confirming a genuine 1-df 2x2 comparison, so convert_to_d()'s 1-df assumption holds cleanly here. Direction=1 because the result favors lysergide (higher abstinence). Note the authors themselves question the validity of this specific comparison (possible 'deprivation effect' inflating the gap via control group I's unusually poor outcomes), which is a substantive caveat for methodologist review even though the statistic itself converts cleanly.</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>0.7523498581074449</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.7422285595678828</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.07371468305722598</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.2715044807313978</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.2100797773343431</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.274377341801423</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Tomsovic 1970</t>
+          <t>Yoon 2019</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1970</v>
+        <v>2019</v>
       </c>
       <c r="C33" t="n">
-        <v>192</v>
+        <v>5</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LSD</t>
+          <t>Ketamine</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Chi-squared</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>7.19</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>chi2</t>
-        </is>
-      </c>
+          <t>Single-arm response rate (%)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>approx</t>
+          <t>excluded</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Primary chi^2 (LSD vs control I, nonschiz, abstinence)</t>
-        </is>
-      </c>
-      <c r="J33" t="n">
-        <v>0.3944861019994785</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0.3929268683947375</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0.0212353945935065</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0.1457236926292581</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0.1073084308413916</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0.6785453059480835</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Yoon 2019</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C34" t="n">
-        <v>5</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Ketamine</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Response rate (%)</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>100</v>
-      </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>excluded</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
           <t>Case series 5/5 response; no comparator</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tables/Alcohol_Tier1_HedgesG.xlsx
+++ b/tables/Alcohol_Tier1_HedgesG.xlsx
@@ -735,7 +735,7 @@
         <v>2019</v>
       </c>
       <c r="C6" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.219</v>
+        <v>0.14</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -762,22 +762,22 @@
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>1.05907456038554</v>
+        <v>0.806946584785929</v>
       </c>
       <c r="K6" t="n">
-        <v>1.030450923618364</v>
+        <v>0.8000496054287843</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1510304850997657</v>
+        <v>0.0480004409508153</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3886264081348123</v>
+        <v>0.2190900293277065</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2687431636741319</v>
+        <v>0.3706331479464796</v>
       </c>
       <c r="O6" t="n">
-        <v>1.792158683562596</v>
+        <v>1.229466062911089</v>
       </c>
     </row>
     <row r="7">
@@ -789,7 +789,9 @@
       <c r="B7" t="n">
         <v>1967</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="n">
+        <v>99</v>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>LSD</t>
@@ -892,7 +894,7 @@
         <v>2022</v>
       </c>
       <c r="C9" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1136,7 +1138,9 @@
       <c r="B14" t="n">
         <v>1969</v>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="n">
+        <v>95</v>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>LSD</t>
@@ -1681,14 +1685,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>OR reported as approx (~5); no cell counts [from 23.5% vs 47.8% (Table 2: ketamine 4/17 vs midazolam 11/23 engaged in at-risk drinking post-infusion)]</t>
+          <t>OR=2.98 computed from Table 2 (ketamine 4/17 vs midazolam 11/23 engaged in at-risk drinking post-infusion), expressed as midazolam:ketamine odds so that &gt;1 already favours ketamine; direction=+1. The frozen entry carried direction=-1 to pair with an OR expressed the other way round, and keeping it after the computed OR was promoted into measure double-negated the sign, plotting a beneficial result as harmful.</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>-0.6020088671595277</v>
+        <v>0.6020088671595277</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.5900484260901332</v>
+        <v>0.5900484260901332</v>
       </c>
       <c r="L25" t="n">
         <v>0.1043519643141431</v>
@@ -1697,10 +1701,10 @@
         <v>0.3230355465179383</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.223198097265292</v>
+        <v>-0.04310124508502577</v>
       </c>
       <c r="O25" t="n">
-        <v>0.04310124508502577</v>
+        <v>1.223198097265292</v>
       </c>
     </row>
     <row r="26">
@@ -1889,7 +1893,7 @@
         <v>2022</v>
       </c>
       <c r="C30" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1923,19 +1927,19 @@
         <v>0.5481600076332798</v>
       </c>
       <c r="K30" t="n">
-        <v>0.5333448722918398</v>
+        <v>0.5383128218674125</v>
       </c>
       <c r="L30" t="n">
-        <v>0.1380742792133333</v>
+        <v>0.09420205334303246</v>
       </c>
       <c r="M30" t="n">
-        <v>0.3715834754309364</v>
+        <v>0.3069235301227856</v>
       </c>
       <c r="N30" t="n">
-        <v>-0.1949587395527955</v>
+        <v>-0.06325729717324724</v>
       </c>
       <c r="O30" t="n">
-        <v>1.261648484136475</v>
+        <v>1.139882940908072</v>
       </c>
     </row>
     <row r="31">
